--- a/output/pdf_financials_xlsx/STND.xlsx
+++ b/output/pdf_financials_xlsx/STND.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.357796</v>
+        <v>-0.357796</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.5181519999999999</v>
@@ -782,16 +782,16 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.036304</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.745</v>
+        <v>-3.11496</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-1.152</v>
+        <v>-7.899808</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.244</v>
+        <v>-2.821188</v>
       </c>
     </row>
     <row r="18">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.357796</v>
+        <v>-0.357796</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.5181519999999999</v>
+        <v>-0.5181519999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.92998</v>
+        <v>-1.92998</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.373904</v>
+        <v>-3.373904</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.288594</v>
+        <v>-1.288594</v>
       </c>
     </row>
     <row r="21">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.357796</v>
+        <v>-0.357796</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.5181519999999999</v>
+        <v>-0.5181519999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.92998</v>
+        <v>-1.92998</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.373904</v>
+        <v>-3.373904</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.288594</v>
+        <v>-1.288594</v>
       </c>
     </row>
     <row r="24">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.357796</v>
+        <v>-0.357796</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.5181519999999999</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.357796</v>
+        <v>-0.357796</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.5181519999999999</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>62.87025941366099</v>
+        <v>262.870259413661</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>25.45347846529666</v>
+        <v>174.5465215347033</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>15.9207200341382</v>
+        <v>184.0792799658618</v>
       </c>
     </row>
     <row r="32">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>3.373904</v>
+        <v>-3.373904</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>1.288594</v>
+        <v>-1.288594</v>
       </c>
     </row>
     <row r="137">
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1.92998</v>
+        <v>-1.92998</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>3.373904</v>
+        <v>-3.373904</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0.5181519999999999</v>
+        <v>-0.5181519999999999</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.357796</v>
+        <v>-0.357796</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.845089</v>
+        <v>-0.845089</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STND.xlsx
+++ b/output/pdf_financials_xlsx/STND.xlsx
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011134</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009823</v>
       </c>
     </row>
     <row r="13">
@@ -1046,10 +1046,10 @@
         <v>1.18498</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.525904</v>
+        <v>4.537038</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.532594</v>
+        <v>1.542417</v>
       </c>
     </row>
     <row r="28">
@@ -1090,10 +1090,10 @@
         <v>1.18498</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.525904</v>
+        <v>4.537038</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.532594</v>
+        <v>1.542417</v>
       </c>
     </row>
     <row r="30">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.283575</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.777069</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.028029</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.555912</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.034389</v>
       </c>
     </row>
     <row r="35">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.283575</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.777069</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.028029</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.385288</v>
+        <v>0.9412</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.04105</v>
+        <v>0.07543900000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1504,19 +1504,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.53947</v>
+        <v>0.255895</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.8320689999999999</v>
+        <v>0.055</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.209188</v>
+        <v>0.181159</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.757787</v>
+        <v>0.201875</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.155617</v>
+        <v>0.121228</v>
       </c>
     </row>
     <row r="49">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">

--- a/output/pdf_financials_xlsx/STND.xlsx
+++ b/output/pdf_financials_xlsx/STND.xlsx
@@ -785,13 +785,13 @@
         <v>-1.036304</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-3.11496</v>
+        <v>-0.745</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-7.899808</v>
+        <v>1.152</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-2.821188</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="18">
@@ -1141,13 +1141,13 @@
         <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>262.870259413661</v>
+        <v>62.87025941366099</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>174.5465215347033</v>
+        <v>25.45347846529666</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>184.0792799658618</v>
+        <v>15.9207200341382</v>
       </c>
     </row>
     <row r="32">
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.240585</v>
       </c>
     </row>
     <row r="116">
@@ -6064,7 +6064,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -6452,7 +6456,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7299,7 +7307,11 @@
           <t>Deferred income tax expense 148,000</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8986,7 +8998,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -10124,7 +10140,11 @@
           <t>Deferred income tax (recovery) expense (Note 14)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
